--- a/tests/data/synthetic-cells/overflow.xlsx
+++ b/tests/data/synthetic-cells/overflow.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Plain" sheetId="1" r:id="rId1"/>
     <sheet name="Lengths" sheetId="2" r:id="rId2"/>
+    <sheet name="Late" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -145,4 +146,21 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="1">
+        <v>1000000000000</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>